--- a/models/xls/BeModelProcedure.xlsx
+++ b/models/xls/BeModelProcedure.xlsx
@@ -500,7 +500,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -936,23 +935,11 @@
           <t>Data Element</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Common Glossary</t>
         </is>
       </c>
-      <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Example Value</t>
@@ -1073,6 +1060,16 @@
           <t>*</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>BusinessIdentifier</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1108,6 +1105,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>RecordedDate</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1178,6 +1185,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1213,6 +1230,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Recorder</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1248,6 +1275,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Performer</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1318,6 +1355,16 @@
           <t>*</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PartOf</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1353,6 +1400,16 @@
           <t>*</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1423,6 +1480,16 @@
           <t>*</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UsedDevice</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1458,6 +1525,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1493,6 +1570,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1633,6 +1720,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>BodyLocation</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1806,6 +1903,16 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>*</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>equivalent</t>
         </is>
       </c>
     </row>
